--- a/myPortfolioManagement/Data/list_of_funds.xlsx
+++ b/myPortfolioManagement/Data/list_of_funds.xlsx
@@ -51,6 +51,960 @@
     <t xml:space="preserve">Type </t>
   </si>
   <si>
+    <t xml:space="preserve">Aegon Global Equity Market Neutral Fund</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aegon Market Neutral</t>
+  </si>
+  <si>
+    <t>IE00BYZJ2252</t>
+  </si>
+  <si>
+    <t>0P00017ZFF.L</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>T</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Allianz Strategic Bond Fund</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Allianz Strategic Bond</t>
+  </si>
+  <si>
+    <t>GB00B06T9362</t>
+  </si>
+  <si>
+    <t>0P00001QSS.L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strategic Bond</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strategic Bonds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Allianz Technology Trust</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Allianz Technology</t>
+  </si>
+  <si>
+    <t>GB00BNG2M159</t>
+  </si>
+  <si>
+    <t>ATT.L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Global Technology</t>
+  </si>
+  <si>
+    <t>Equity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALPS Clean Energy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALPS Cln Energy</t>
+  </si>
+  <si>
+    <t>ACES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Artemis UK Select Fund Class I Acc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Artemis UK</t>
+  </si>
+  <si>
+    <t>GB00B2PLJG05</t>
+  </si>
+  <si>
+    <t>0P0000V25A.L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASI Global Absolute Return Strategies Fund Platform 1 Accumulation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASI Abs Returns</t>
+  </si>
+  <si>
+    <t>GB00B7K3T226</t>
+  </si>
+  <si>
+    <t>0P0000WUQG.L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASI Global Smaller Companies Fund</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASI Small Cap</t>
+  </si>
+  <si>
+    <t>GB00B7KVX245</t>
+  </si>
+  <si>
+    <t>0P0000WUOL.L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Global Small Cap</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASI UK Real Estate Share Fund</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASI UK Real Estate</t>
+  </si>
+  <si>
+    <t>GB00B0XWNN66</t>
+  </si>
+  <si>
+    <t>0P0000XOMY.L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AXA Framlington Managed Income Fund Z Gross GBP Acc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AXA Income</t>
+  </si>
+  <si>
+    <t>GB00B7H1PG56</t>
+  </si>
+  <si>
+    <t>0P0000XMS3.L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Baillie Gifford American Fund B Accumulation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BG American</t>
+  </si>
+  <si>
+    <t>GB0006061963</t>
+  </si>
+  <si>
+    <t>0P00000VC9.L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Baillie Gifford European B Acc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BG European</t>
+  </si>
+  <si>
+    <t>GB0006058258</t>
+  </si>
+  <si>
+    <t>0P00000QWM.L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Baillie Gifford Global Alpha</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BG Alpha</t>
+  </si>
+  <si>
+    <t>GB00B61DJ021</t>
+  </si>
+  <si>
+    <t>0P0000NMRS.L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Baillie Gifford Global Discovery Fund B Accumulation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BG Discovery</t>
+  </si>
+  <si>
+    <t>GB0006059330</t>
+  </si>
+  <si>
+    <t>0P00000VC8.L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Baillie Gifford Global Income Growth Fund B Acc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BG Income</t>
+  </si>
+  <si>
+    <t>GB0005772479</t>
+  </si>
+  <si>
+    <t>0P00000VC6.L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Global Equities Income</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Baillie Gifford Managed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BG Managed</t>
+  </si>
+  <si>
+    <t>GB0006010168</t>
+  </si>
+  <si>
+    <t>0P00000QWU.L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Baillie Gifford Pacific Fund B Acc</t>
+  </si>
+  <si>
+    <t>GB0006063233</t>
+  </si>
+  <si>
+    <t>0P00000QWJ.L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asia Pacific</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Baillie Gifford Positive Change Fund B Accumulation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BG Positive Change</t>
+  </si>
+  <si>
+    <t>GB00BYVGKV59</t>
+  </si>
+  <si>
+    <t>0P0001BDIT.L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Global ESG Equities</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barings Global Agriculture Fund - Class I GBP Acc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Baring Agri</t>
+  </si>
+  <si>
+    <t>GB00B3B9VD63</t>
+  </si>
+  <si>
+    <t>0P0000J1C2.L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BlackRock Continental European Income</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BLR European</t>
+  </si>
+  <si>
+    <t>GB00BWG07178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BlackRock European Absolute Alpha</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BLR Abs Ret European</t>
+  </si>
+  <si>
+    <t>GB00B4Y62W78</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BlackRock Global Funds - World Mining Fund D2 GBP Hedged</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BLR Mining</t>
+  </si>
+  <si>
+    <t>LU0827890145</t>
+  </si>
+  <si>
+    <t>BRWM.L</t>
+  </si>
+  <si>
+    <t>Commodities</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BlackRock Throgmorton Trust plc (THRG)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Throgmorton Trust</t>
+  </si>
+  <si>
+    <t>GB0008910555</t>
+  </si>
+  <si>
+    <t>THRG.L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UK Small Cap</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BlackRock World Mining Trust Ord</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fidelity China Special Situations PLC (FCSS)</t>
+  </si>
+  <si>
+    <t>FCSS</t>
+  </si>
+  <si>
+    <t>GB00B62Z3C74</t>
+  </si>
+  <si>
+    <t>FCSS.L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fidelity Funds - Global Financial Services Fund W-Acc-GBP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fidelity Global Fin</t>
+  </si>
+  <si>
+    <t>LU1033663136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fidelity Funds - Global Technology Fund W-Acc-GBP</t>
+  </si>
+  <si>
+    <t>LU1033663649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fidelity Funds - Sustainable Water &amp; Waste Fund W Acc GBP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fidelity Water</t>
+  </si>
+  <si>
+    <t>LU1892829745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fidelity Global Special Situations Fund W Acc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fidelity Global Sit</t>
+  </si>
+  <si>
+    <t>GB00B8HT7153</t>
+  </si>
+  <si>
+    <t>0P0000WUT6.L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Global Equities</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fidelity Special Situations Fund W-Accumulation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fidelity Special Situations</t>
+  </si>
+  <si>
+    <t>GB00B88V3X40</t>
+  </si>
+  <si>
+    <t>0P0000WUU1.L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">First Sentier Global Infrastructure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FS Infrast</t>
+  </si>
+  <si>
+    <t>GB00B8PLJ176</t>
+  </si>
+  <si>
+    <t>0P00009VDH.L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">First Trust NASDAQ CEA Cybersecurity ETF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nasdaq Cybersecurity</t>
+  </si>
+  <si>
+    <t>CIBR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">First Trust NASDAQ Clean Edge Smart Infrastructure Index Fund</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clean Infra</t>
+  </si>
+  <si>
+    <t>GRID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FP Foresight UK Infrastructure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FP UK infrastructure</t>
+  </si>
+  <si>
+    <t>GB00BF0VS922</t>
+  </si>
+  <si>
+    <t>0P0001BSDU.L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FP Octopus UK Micro Cap Growth Fund</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Octopus Small Cap</t>
+  </si>
+  <si>
+    <t>GB00BYQ7HN43</t>
+  </si>
+  <si>
+    <t>0P00018QYX.L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fundsmith Equity I Acc</t>
+  </si>
+  <si>
+    <t>Fundsmith</t>
+  </si>
+  <si>
+    <t>GB00B41YBW71</t>
+  </si>
+  <si>
+    <t>0P0000RU81.L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HSBC MSCI Taiwan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HSBC Taiwan</t>
+  </si>
+  <si>
+    <t>HTWN.L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HSBC Pacific Index Fund Accumulation C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pacific Index</t>
+  </si>
+  <si>
+    <t>GB00B80QGT40</t>
+  </si>
+  <si>
+    <t>0P0000WN7N.L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Invesco S&amp;P Global Water Index ETF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Global Water</t>
+  </si>
+  <si>
+    <t>CGW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iShares 20+ Year Treasury Bond</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US 20 Year Bonds</t>
+  </si>
+  <si>
+    <t>TLT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iShares 3-7 Year Treasury Bond</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US 3-7 Year Bonds</t>
+  </si>
+  <si>
+    <t>IEI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iShares Core MSCI Emerging Markets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Core EM ETF</t>
+  </si>
+  <si>
+    <t>IEMG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iShares Core S&amp;P 500 ETF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S&amp;P Core</t>
+  </si>
+  <si>
+    <t>IVV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iShares Core S&amp;P Mid-Cap</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S&amp;P Mid-Cap</t>
+  </si>
+  <si>
+    <t>IJH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iShares Core S&amp;P Small-Cap</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Core S&amp;P Small-Cap</t>
+  </si>
+  <si>
+    <t>IJR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US Small Cap</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iShares Core S&amp;P Total US Stock Mkt ETF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Core S&amp;P ETF</t>
+  </si>
+  <si>
+    <t>ITOT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iShares Emerging Markets Infrastructure ETF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EM infra ETF</t>
+  </si>
+  <si>
+    <t>EMIF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iShares ESG MSCI USA ETF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ESG USA</t>
+  </si>
+  <si>
+    <t>ESGU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iShares Global Infrastructure ETF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Global Infra ETF</t>
+  </si>
+  <si>
+    <t>IGF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iShares Global Water ETF USD Dist GBP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iShares Index-Linked Gilts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Global Linkers</t>
+  </si>
+  <si>
+    <t>INXG.L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iShares MSCI EAFE Growth ETF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MSCI Growth ETF</t>
+  </si>
+  <si>
+    <t>EFG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iShares MSCI EAFE Value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MSCI Value ETF</t>
+  </si>
+  <si>
+    <t>EFV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iShares S&amp;P 500 Growth ETF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S&amp;P Growth</t>
+  </si>
+  <si>
+    <t>IVW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iShares S&amp;P 500 Value ETF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S&amp;P Value</t>
+  </si>
+  <si>
+    <t>IVE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iShares S&amp;P Mid-Cap 400 Growth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S&amp;P Mid-Cap Growth</t>
+  </si>
+  <si>
+    <t>IJK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iShares S&amp;P MidCap 400 Value ETF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S&amp;P Mid-Cap Value</t>
+  </si>
+  <si>
+    <t>IJJ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iShares U.S. Infrastructure ETF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US infra ETF</t>
+  </si>
+  <si>
+    <t>IFRA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iShares U.S. Real Estate ETF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US REITs</t>
+  </si>
+  <si>
+    <t>IYR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Janus Henderson European Absolute Return Fund I Acc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JH European Abs Returns</t>
+  </si>
+  <si>
+    <t>GB00B3CPX375</t>
+  </si>
+  <si>
+    <t>0P0000HRXV.L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Janus Henderson Multi-Asset Absolute Return Fund I Acc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JH Abs Returns</t>
+  </si>
+  <si>
+    <t>GB00B8113P38</t>
+  </si>
+  <si>
+    <t>0P0000WM8Q.L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Market Neutral</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JPM Global Macro Opportunities Fund C - Net Accumulation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JPM Global Macro</t>
+  </si>
+  <si>
+    <t>GB00B4WKYF80</t>
+  </si>
+  <si>
+    <t>0P0000Y1OB.L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jupiter Merian Global Equity Absolute Return Fund I GBP Hedged Acc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JM Global Abs Returns</t>
+  </si>
+  <si>
+    <t>IE00BLP5S809</t>
+  </si>
+  <si>
+    <t>0P0001339G.L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jupiter Merian Strategic Absolute Rtrn Bond</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jupiter Absolute Return Bond</t>
+  </si>
+  <si>
+    <t>IE00BF1F1K54</t>
+  </si>
+  <si>
+    <t>0P0001D17E.L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L&amp;G Battery Value-Chain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L&amp;G Value-Chain</t>
+  </si>
+  <si>
+    <t>BATG.L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Legg Mason Royce US Small Cap Opportunity Fund</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LMR US Small Cap</t>
+  </si>
+  <si>
+    <t>IE00B23Z8V29</t>
+  </si>
+  <si>
+    <t>0P0000YU6F.L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M&amp;G Global Themes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M&amp;G Themes</t>
+  </si>
+  <si>
+    <t>GB00B4WV2P70</t>
+  </si>
+  <si>
+    <t>0P0000WN2U.L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M&amp;G North American Value Fund Sterling I Acc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M&amp;G US Value</t>
+  </si>
+  <si>
+    <t>GB00B61S4242</t>
+  </si>
+  <si>
+    <t>0P0000WN4G.L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Merian Global Strategic Bond Fund I GBP Inc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Merian Strategic Bond</t>
+  </si>
+  <si>
+    <t>GB00B1XG8J69</t>
+  </si>
+  <si>
+    <t>0P0000PP48.L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MI Chelverton UK Equity Growth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MI UK Growth</t>
+  </si>
+  <si>
+    <t>GB00BP855B75</t>
+  </si>
+  <si>
+    <t>0P00014IJX.L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nordea 1 - GBP Diversified Return Fund BC GBP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nordea Abs Return</t>
+  </si>
+  <si>
+    <t>LU1224690856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pacific Horizon Ord</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pacific Horizon</t>
+  </si>
+  <si>
+    <t>GB0006667470</t>
+  </si>
+  <si>
+    <t>PHI.L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pictet - Global Environmental Opportunities I dy GBP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pictet Climate</t>
+  </si>
+  <si>
+    <t>LU0503632878</t>
+  </si>
+  <si>
+    <t>Climate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PowerShares EQQQ Nasdaq-100 UCITS</t>
+  </si>
+  <si>
+    <t>Nasdaq</t>
+  </si>
+  <si>
+    <t>EQGB.L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rathbone Ethical Bond Fund Institutional Inc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rathbone Ethical Bonds</t>
+  </si>
+  <si>
+    <t>GB00B7FQJT36</t>
+  </si>
+  <si>
+    <t>0P0000VDY9.L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rathbone Global Opportunities Fund S Acc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rathbone Global</t>
+  </si>
+  <si>
+    <t>GB00BH0P2M97</t>
+  </si>
+  <si>
+    <t>0P0001FE43.L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rathbone Multi Asset Strategic Growth Portfolio S-Class Accumulation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rathbone Multi-Asset</t>
+  </si>
+  <si>
+    <t>GB00B86QF242</t>
+  </si>
+  <si>
+    <t>0P0000X4CD.L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Volatility Managed</t>
+  </si>
+  <si>
+    <t>Multi-Asset</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RobecoSAM Sustainable Water Equities I GBP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rebeco Water</t>
+  </si>
+  <si>
+    <t>LU2146192450</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Royal London Sterling Extra Yield Bond Fund A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RL Yield Bond</t>
+  </si>
+  <si>
+    <t>IE0032571485</t>
+  </si>
+  <si>
+    <t>0P000023IY.L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Royal London Sustainable Diversified Trust</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RL Diversified</t>
+  </si>
+  <si>
+    <t>GB00B79LTQ12</t>
+  </si>
+  <si>
+    <t>0P0000XYWO.L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sanlam Multi Strategy Fund A GBP Accumulation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sanlam Multi-Strategy</t>
+  </si>
+  <si>
+    <t>IE00B4QNLR45</t>
+  </si>
+  <si>
+    <t>0P00012DMS.L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scottish Mortgage Ord</t>
+  </si>
+  <si>
+    <t>SMT</t>
+  </si>
+  <si>
+    <t>GB00BLDYK618</t>
+  </si>
+  <si>
+    <t>SMT.L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stewart Investors Asia Pacific Leaders Sustainability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stewart Asia Leaders</t>
+  </si>
+  <si>
+    <t>GB0033874768</t>
+  </si>
+  <si>
+    <t>0P00000H6Q.L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Threadneedle (Lux) - Global Smaller Companies ZGH (GBP Accumulation Hedged Shares)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Threadneedle Global Small</t>
+  </si>
+  <si>
+    <t>LU0815285274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TM RWC UK Equity Income</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TM RWC UK</t>
+  </si>
+  <si>
+    <t>GB00BG341295</t>
+  </si>
+  <si>
+    <t>0P0001E0SF.L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trojan Fund X Accumulation</t>
+  </si>
+  <si>
+    <t>Trojan</t>
+  </si>
+  <si>
+    <t>GB00BZ6CNS31</t>
+  </si>
+  <si>
+    <t>0P0001CBJA.L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vanguard ESG U.S. Stock ETF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ESG USA Vanguard</t>
+  </si>
+  <si>
+    <t>ESGV</t>
+  </si>
+  <si>
     <t xml:space="preserve">Vanguard FTSE All-World UCITS ETF</t>
   </si>
   <si>
@@ -60,346 +1014,52 @@
     <t>VWRL.L</t>
   </si>
   <si>
-    <t>F</t>
-  </si>
-  <si>
-    <t>T</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iShares 20+ Year Treasury Bond</t>
-  </si>
-  <si>
-    <t xml:space="preserve">US 20 Year Bonds</t>
-  </si>
-  <si>
-    <t>TLT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Baillie Gifford Pacific Fund B Acc</t>
-  </si>
-  <si>
-    <t>GB0006063233</t>
-  </si>
-  <si>
-    <t>0P00000QWJ.L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Asia Pacific</t>
-  </si>
-  <si>
-    <t>Equity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pacific Horizon Ord</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pacific Horizon</t>
-  </si>
-  <si>
-    <t>GB0006667470</t>
-  </si>
-  <si>
-    <t>PHI.L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stewart Investors Asia Pacific Leaders Sustainability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stewart Asia Leaders</t>
-  </si>
-  <si>
-    <t>GB0033874768</t>
-  </si>
-  <si>
-    <t>0P00000H6Q.L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iShares U.S. Real Estate ETF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">US REITs</t>
-  </si>
-  <si>
-    <t>IYR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iShares S&amp;P 500 Growth ETF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S&amp;P Growth</t>
-  </si>
-  <si>
-    <t>IVW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iShares Core S&amp;P 500 ETF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S&amp;P Core</t>
-  </si>
-  <si>
-    <t>IVV</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iShares S&amp;P 500 Value ETF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S&amp;P Value</t>
-  </si>
-  <si>
-    <t>IVE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iShares Core S&amp;P Total US Stock Mkt ETF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Core S&amp;P ETF</t>
-  </si>
-  <si>
-    <t>ITOT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iShares Index-Linked Gilts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Global Linkers</t>
-  </si>
-  <si>
-    <t>INXG.L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iShares S&amp;P Mid-Cap 400 Growth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S&amp;P Mid-Cap Growth</t>
-  </si>
-  <si>
-    <t>IJK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iShares S&amp;P MidCap 400 Value ETF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S&amp;P Mid-Cap Value</t>
-  </si>
-  <si>
-    <t>IJJ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iShares Core S&amp;P Mid-Cap</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S&amp;P Mid-Cap</t>
-  </si>
-  <si>
-    <t>IJH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iShares Global Infrastructure ETF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Global Infra ETF</t>
-  </si>
-  <si>
-    <t>IGF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iShares U.S. Infrastructure ETF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">US infra ETF</t>
-  </si>
-  <si>
-    <t>IFRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iShares Core MSCI Emerging Markets</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Core EM ETF</t>
-  </si>
-  <si>
-    <t>IEMG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iShares 3-7 Year Treasury Bond</t>
-  </si>
-  <si>
-    <t xml:space="preserve">US 3-7 Year Bonds</t>
-  </si>
-  <si>
-    <t>IEI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HSBC MSCI Taiwan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HSBC Taiwan</t>
-  </si>
-  <si>
-    <t>HTWN.L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">First Trust NASDAQ Clean Edge Smart Infrastructure Index Fund</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clean Infra</t>
-  </si>
-  <si>
-    <t>GRID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fidelity China Special Situations PLC (FCSS)</t>
-  </si>
-  <si>
-    <t>FCSS</t>
-  </si>
-  <si>
-    <t>GB00B62Z3C74</t>
-  </si>
-  <si>
-    <t>FCSS.L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vanguard ESG U.S. Stock ETF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ESG USA Vanguard</t>
-  </si>
-  <si>
-    <t>ESGV</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iShares ESG MSCI USA ETF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ESG USA</t>
-  </si>
-  <si>
-    <t>ESGU</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PowerShares EQQQ Nasdaq-100 UCITS</t>
-  </si>
-  <si>
-    <t>Nasdaq</t>
-  </si>
-  <si>
-    <t>EQGB.L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iShares Emerging Markets Infrastructure ETF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EM infra ETF</t>
-  </si>
-  <si>
-    <t>EMIF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iShares MSCI EAFE Value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MSCI Value ETF</t>
-  </si>
-  <si>
-    <t>EFV</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iShares MSCI EAFE Growth ETF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MSCI Growth ETF</t>
-  </si>
-  <si>
-    <t>EFG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">First Trust NASDAQ CEA Cybersecurity ETF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nasdaq Cybersecurity</t>
-  </si>
-  <si>
-    <t>CIBR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Invesco S&amp;P Global Water Index ETF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Global Water</t>
-  </si>
-  <si>
-    <t>CGW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pictet - Global Environmental Opportunities I dy GBP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pictet Climate</t>
-  </si>
-  <si>
-    <t>LU0503632878</t>
-  </si>
-  <si>
-    <t>Climate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L&amp;G Battery Value-Chain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L&amp;G Value-Chain</t>
-  </si>
-  <si>
-    <t>BATG.L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ALPS Clean Energy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ALPS Cln Energy</t>
-  </si>
-  <si>
-    <t>ACES</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BlackRock Global Funds - World Mining Fund D2 GBP Hedged</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BLR Mining</t>
-  </si>
-  <si>
-    <t>LU0827890145</t>
-  </si>
-  <si>
-    <t>BRWM.L</t>
-  </si>
-  <si>
-    <t>Commodities</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TM RWC UK Equity Income</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TM RWC UK</t>
-  </si>
-  <si>
-    <t>GB00BG341295</t>
-  </si>
-  <si>
-    <t>0P0001E0SF.L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FP Foresight UK Infrastructure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FP UK infrastructure</t>
-  </si>
-  <si>
-    <t>GB00BF0VS922</t>
-  </si>
-  <si>
-    <t>0P0001BSDU.L</t>
+    <t xml:space="preserve">Vanguard FTSE Developed World ex-U.K. Equity Index Fund GBP Acc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">World ex-UK</t>
+  </si>
+  <si>
+    <t>GB00B59G4Q73</t>
+  </si>
+  <si>
+    <t>0P0000KSP6.L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vanguard Global Bond Index Fund GBP Hedged Acc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Global Bond</t>
+  </si>
+  <si>
+    <t>IE00B50W2R13</t>
+  </si>
+  <si>
+    <t>0P0000KM24.L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vanguard Global Small-Cap Index Fund GBP Acc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vanguard Global Small Cap</t>
+  </si>
+  <si>
+    <t>IE00B3X1NT05</t>
+  </si>
+  <si>
+    <t>0P0000N47O.L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VT Argonaut Absolute Return Fund Class R (currency hedged) Retail GBP Net Accumulation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VT Absolute Alpha</t>
+  </si>
+  <si>
+    <t>GB00B7FT1K78</t>
+  </si>
+  <si>
+    <t>0P0000W526.L</t>
   </si>
   <si>
     <t xml:space="preserve">WisdomTree Physical Gold (PHGP)</t>
@@ -414,666 +1074,6 @@
     <t>PHGP.L</t>
   </si>
   <si>
-    <t xml:space="preserve">FP Octopus UK Micro Cap Growth Fund</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Octopus Small Cap</t>
-  </si>
-  <si>
-    <t>GB00BYQ7HN43</t>
-  </si>
-  <si>
-    <t>0P00018QYX.L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aegon Global Equity Market Neutral Fund</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aegon Market Neutral</t>
-  </si>
-  <si>
-    <t>IE00BYZJ2252</t>
-  </si>
-  <si>
-    <t>0P00017ZFF.L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fundsmith Equity I Acc</t>
-  </si>
-  <si>
-    <t>Fundsmith</t>
-  </si>
-  <si>
-    <t>GB00B41YBW71</t>
-  </si>
-  <si>
-    <t>0P0000RU81.L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Global Equities</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jupiter Merian Global Equity Absolute Return Fund I GBP Hedged Acc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JM Global Abs Returns</t>
-  </si>
-  <si>
-    <t>IE00BLP5S809</t>
-  </si>
-  <si>
-    <t>0P0001339G.L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sanlam Multi Strategy Fund A GBP Accumulation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sanlam Multi-Strategy</t>
-  </si>
-  <si>
-    <t>IE00B4QNLR45</t>
-  </si>
-  <si>
-    <t>0P00012DMS.L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Legg Mason Royce US Small Cap Opportunity Fund</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LMR US Small Cap</t>
-  </si>
-  <si>
-    <t>IE00B23Z8V29</t>
-  </si>
-  <si>
-    <t>0P0000YU6F.L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JPM Global Macro Opportunities Fund C - Net Accumulation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JPM Global Macro</t>
-  </si>
-  <si>
-    <t>GB00B4WKYF80</t>
-  </si>
-  <si>
-    <t>0P0000Y1OB.L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ASI UK Real Estate Share Fund</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ASI UK Real Estate</t>
-  </si>
-  <si>
-    <t>GB00B0XWNN66</t>
-  </si>
-  <si>
-    <t>0P0000XOMY.L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AXA Framlington Managed Income Fund Z Gross GBP Acc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AXA Income</t>
-  </si>
-  <si>
-    <t>GB00B7H1PG56</t>
-  </si>
-  <si>
-    <t>0P0000XMS3.L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fidelity Special Situations Fund W-Accumulation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fidelity Special Situations</t>
-  </si>
-  <si>
-    <t>GB00B88V3X40</t>
-  </si>
-  <si>
-    <t>0P0000WUU1.L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ASI Global Absolute Return Strategies Fund Platform 1 Accumulation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ASI Abs Returns</t>
-  </si>
-  <si>
-    <t>GB00B7K3T226</t>
-  </si>
-  <si>
-    <t>0P0000WUQG.L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HSBC Pacific Index Fund Accumulation C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pacific Index</t>
-  </si>
-  <si>
-    <t>GB00B80QGT40</t>
-  </si>
-  <si>
-    <t>0P0000WN7N.L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M&amp;G North American Value Fund Sterling I Acc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M&amp;G US Value</t>
-  </si>
-  <si>
-    <t>GB00B61S4242</t>
-  </si>
-  <si>
-    <t>0P0000WN4G.L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M&amp;G Global Themes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M&amp;G Themes</t>
-  </si>
-  <si>
-    <t>GB00B4WV2P70</t>
-  </si>
-  <si>
-    <t>0P0000WN2U.L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vanguard FTSE Developed World ex-U.K. Equity Index Fund GBP Acc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">World ex-UK</t>
-  </si>
-  <si>
-    <t>GB00B59G4Q73</t>
-  </si>
-  <si>
-    <t>0P0000KSP6.L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vanguard Global Bond Index Fund GBP Hedged Acc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Global Bond</t>
-  </si>
-  <si>
-    <t>IE00B50W2R13</t>
-  </si>
-  <si>
-    <t>0P0000KM24.L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Barings Global Agriculture Fund - Class I GBP Acc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Baring Agri</t>
-  </si>
-  <si>
-    <t>GB00B3B9VD63</t>
-  </si>
-  <si>
-    <t>0P0000J1C2.L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Janus Henderson European Absolute Return Fund I Acc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JH European Abs Returns</t>
-  </si>
-  <si>
-    <t>GB00B3CPX375</t>
-  </si>
-  <si>
-    <t>0P0000HRXV.L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">First Sentier Global Infrastructure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FS Infrast</t>
-  </si>
-  <si>
-    <t>GB00B8PLJ176</t>
-  </si>
-  <si>
-    <t>0P00009VDH.L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Baillie Gifford American Fund B Accumulation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BG American</t>
-  </si>
-  <si>
-    <t>GB0006061963</t>
-  </si>
-  <si>
-    <t>0P00000VC9.L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fidelity Global Special Situations Fund W Acc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fidelity Global Sit</t>
-  </si>
-  <si>
-    <t>GB00B8HT7153</t>
-  </si>
-  <si>
-    <t>0P0000WUT6.L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Baillie Gifford Managed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BG Managed</t>
-  </si>
-  <si>
-    <t>GB0006010168</t>
-  </si>
-  <si>
-    <t>0P00000QWU.L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rathbone Global Opportunities Fund S Acc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rathbone Global</t>
-  </si>
-  <si>
-    <t>GB00BH0P2M97</t>
-  </si>
-  <si>
-    <t>0P0001FE43.L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Scottish Mortgage Ord</t>
-  </si>
-  <si>
-    <t>SMT</t>
-  </si>
-  <si>
-    <t>GB00BLDYK618</t>
-  </si>
-  <si>
-    <t>SMT.L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Artemis UK Select Fund Class I Acc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Artemis UK</t>
-  </si>
-  <si>
-    <t>GB00B2PLJG05</t>
-  </si>
-  <si>
-    <t>0P0000V25A.L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Baillie Gifford European B Acc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BG European</t>
-  </si>
-  <si>
-    <t>GB0006058258</t>
-  </si>
-  <si>
-    <t>0P00000QWM.L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Baillie Gifford Global Alpha</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BG Alpha</t>
-  </si>
-  <si>
-    <t>GB00B61DJ021</t>
-  </si>
-  <si>
-    <t>0P0000NMRS.L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Baillie Gifford Global Income Growth Fund B Acc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BG Income</t>
-  </si>
-  <si>
-    <t>GB0005772479</t>
-  </si>
-  <si>
-    <t>0P00000VC6.L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Global Equities Income</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BlackRock Continental European Income</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BLR European</t>
-  </si>
-  <si>
-    <t>GB00BWG07178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BlackRock European Absolute Alpha</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BLR Abs Ret European</t>
-  </si>
-  <si>
-    <t>GB00B4Y62W78</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fidelity Funds - Global Financial Services Fund W-Acc-GBP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fidelity Global Fin</t>
-  </si>
-  <si>
-    <t>LU1033663136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Baillie Gifford Positive Change Fund B Accumulation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BG Positive Change</t>
-  </si>
-  <si>
-    <t>GB00BYVGKV59</t>
-  </si>
-  <si>
-    <t>0P0001BDIT.L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Global ESG Equities</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fidelity Funds - Sustainable Water &amp; Waste Fund W Acc GBP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fidelity Water</t>
-  </si>
-  <si>
-    <t>LU1892829745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Baillie Gifford Global Discovery Fund B Accumulation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BG Discovery</t>
-  </si>
-  <si>
-    <t>GB0006059330</t>
-  </si>
-  <si>
-    <t>0P00000VC8.L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Global Small Cap</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nordea 1 - GBP Diversified Return Fund BC GBP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nordea Abs Return</t>
-  </si>
-  <si>
-    <t>LU1224690856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RobecoSAM Sustainable Water Equities I GBP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rebeco Water</t>
-  </si>
-  <si>
-    <t>LU2146192450</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Threadneedle (Lux) - Global Smaller Companies ZGH (GBP Accumulation Hedged Shares)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Threadneedle Global Small</t>
-  </si>
-  <si>
-    <t>LU0815285274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ASI Global Smaller Companies Fund</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ASI Small Cap</t>
-  </si>
-  <si>
-    <t>GB00B7KVX245</t>
-  </si>
-  <si>
-    <t>0P0000WUOL.L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vanguard Global Small-Cap Index Fund GBP Acc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vanguard Global Small Cap</t>
-  </si>
-  <si>
-    <t>IE00B3X1NT05</t>
-  </si>
-  <si>
-    <t>0P0000N47O.L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Allianz Technology Trust</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Allianz Technology</t>
-  </si>
-  <si>
-    <t>GB00BNG2M159</t>
-  </si>
-  <si>
-    <t>ATT.L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Global Technology</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fidelity Funds - Global Technology Fund W-Acc-GBP</t>
-  </si>
-  <si>
-    <t>LU1033663649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Janus Henderson Multi-Asset Absolute Return Fund I Acc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JH Abs Returns</t>
-  </si>
-  <si>
-    <t>GB00B8113P38</t>
-  </si>
-  <si>
-    <t>0P0000WM8Q.L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Market Neutral</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jupiter Merian Strategic Absolute Rtrn Bond</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jupiter Absolute Return Bond</t>
-  </si>
-  <si>
-    <t>IE00BF1F1K54</t>
-  </si>
-  <si>
-    <t>0P0001D17E.L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Merian Global Strategic Bond Fund I GBP Inc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Merian Strategic Bond</t>
-  </si>
-  <si>
-    <t>GB00B1XG8J69</t>
-  </si>
-  <si>
-    <t>0P0000PP48.L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strategic Bond</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strategic Bonds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Allianz Strategic Bond Fund</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Allianz Strategic Bond</t>
-  </si>
-  <si>
-    <t>GB00B06T9362</t>
-  </si>
-  <si>
-    <t>0P00001QSS.L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Royal London Sterling Extra Yield Bond Fund A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RL Yield Bond</t>
-  </si>
-  <si>
-    <t>IE0032571485</t>
-  </si>
-  <si>
-    <t>0P000023IY.L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rathbone Ethical Bond Fund Institutional Inc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rathbone Ethical Bonds</t>
-  </si>
-  <si>
-    <t>GB00B7FQJT36</t>
-  </si>
-  <si>
-    <t>0P0000VDY9.L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MI Chelverton UK Equity Growth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MI UK Growth</t>
-  </si>
-  <si>
-    <t>GB00BP855B75</t>
-  </si>
-  <si>
-    <t>0P00014IJX.L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UK Small Cap</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BlackRock Throgmorton Trust plc (THRG)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Throgmorton Trust</t>
-  </si>
-  <si>
-    <t>GB0008910555</t>
-  </si>
-  <si>
-    <t>THRG.L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iShares Core S&amp;P Small-Cap</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Core S&amp;P Small-Cap</t>
-  </si>
-  <si>
-    <t>IJR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">US Small Cap</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Royal London Sustainable Diversified Trust</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RL Diversified</t>
-  </si>
-  <si>
-    <t>GB00B79LTQ12</t>
-  </si>
-  <si>
-    <t>0P0000XYWO.L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Volatility Managed</t>
-  </si>
-  <si>
-    <t>Multi-Asset</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rathbone Multi Asset Strategic Growth Portfolio S-Class Accumulation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rathbone Multi-Asset</t>
-  </si>
-  <si>
-    <t>GB00B86QF242</t>
-  </si>
-  <si>
-    <t>0P0000X4CD.L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trojan Fund X Accumulation</t>
-  </si>
-  <si>
-    <t>Trojan</t>
-  </si>
-  <si>
-    <t>GB00BZ6CNS31</t>
-  </si>
-  <si>
-    <t>0P0001CBJA.L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BlackRock World Mining Trust Ord</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iShares Global Water ETF USD Dist GBP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VT Argonaut Absolute Return Fund Class R (currency hedged) Retail GBP Net Accumulation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VT Absolute Alpha</t>
-  </si>
-  <si>
-    <t>GB00B7FT1K78</t>
-  </si>
-  <si>
-    <t>0P0000W526.L</t>
-  </si>
-  <si>
     <t>Asset</t>
   </si>
   <si>
@@ -1173,6 +1173,24 @@
     <t>myfunds</t>
   </si>
   <si>
+    <t xml:space="preserve">HarbourVest Global Private Equity (HVPE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HV Global PE</t>
+  </si>
+  <si>
+    <t>GG00BR30MJ80</t>
+  </si>
+  <si>
+    <t>HVPE.L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Private Equity</t>
+  </si>
+  <si>
+    <t>Alternatives</t>
+  </si>
+  <si>
     <t xml:space="preserve">Legal &amp; General All Stocks Index Linked Gilt Index Trust</t>
   </si>
   <si>
@@ -1228,24 +1246,6 @@
   </si>
   <si>
     <t>ISP6.L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HarbourVest Global Private Equity (HVPE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HV Global PE</t>
-  </si>
-  <si>
-    <t>GG00BR30MJ80</t>
-  </si>
-  <si>
-    <t>HVPE.L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Private Equity</t>
-  </si>
-  <si>
-    <t>Alternatives</t>
   </si>
   <si>
     <t xml:space="preserve">Fidelity Funds - Asian Smaller Companies Fund Y-Acc-GBP</t>
@@ -1621,7 +1621,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1812,18 +1812,6 @@
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.39997558519241899"/>
         <bgColor theme="6" tint="0.39997558519241899"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor theme="4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431398"/>
-        <bgColor theme="4" tint="0.79998168889431398"/>
       </patternFill>
     </fill>
   </fills>
@@ -2127,7 +2115,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2135,15 +2123,16 @@
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf fontId="20" fillId="33" borderId="9" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="20" fillId="33" borderId="10" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="21" fillId="33" borderId="10" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="20" fillId="19" borderId="9" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="20" fillId="19" borderId="10" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="21" fillId="19" borderId="10" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf fontId="21" fillId="33" borderId="11" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="21" fillId="19" borderId="11" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf fontId="2" fillId="34" borderId="12" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="2" fillId="18" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf fontId="2" fillId="0" borderId="12" numFmtId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="9" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2256,8 +2245,8 @@
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" displayName="Table3" ref="A1:J94">
   <autoFilter ref="A1:J94"/>
-  <sortState ref="A1:J94">
-    <sortCondition ref="I1"/>
+  <sortState ref="A1:A94">
+    <sortCondition descending="0" ref="A1:A94"/>
   </sortState>
   <tableColumns count="10">
     <tableColumn id="1" name="fund"/>
@@ -2278,8 +2267,8 @@
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" displayName="Table2" ref="A1:G40">
   <autoFilter ref="A1:G40"/>
-  <sortState ref="A1:G40">
-    <sortCondition ref="F1"/>
+  <sortState ref="F1:F40">
+    <sortCondition descending="0" ref="F1:F40"/>
   </sortState>
   <tableColumns count="7">
     <tableColumn id="1" name="fund"/>
@@ -2792,11 +2781,11 @@
   </sheetPr>
   <sheetFormatPr defaultColWidth="8.9411764705882408" defaultRowHeight="16.5"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="75.235294117647101"/>
-    <col customWidth="1" min="2" max="2" width="24.764705882352899"/>
-    <col customWidth="1" min="3" max="3" width="15.823529411764699"/>
+    <col bestFit="1" customWidth="1" min="1" max="1" width="68.00390625"/>
+    <col bestFit="1" customWidth="1" min="2" max="2" width="22.43359375"/>
+    <col bestFit="1" customWidth="1" min="3" max="3" width="13.43359375"/>
     <col customWidth="1" min="4" max="4" width="17.0588235294118"/>
-    <col customWidth="1" min="5" max="5" width="5.5294117647058796"/>
+    <col bestFit="1" customWidth="1" min="5" max="5" width="6.68359375"/>
     <col customWidth="1" min="6" max="6" width="4.6470588235294104"/>
     <col customWidth="1" min="7" max="7" width="12.176470588235301"/>
     <col customWidth="1" min="8" max="8" width="14.588235294117601"/>
@@ -2842,21 +2831,23 @@
       <c r="B2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="1"/>
+      <c r="C2" s="1" t="s">
+        <v>12</v>
+      </c>
       <c r="D2" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>14</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
@@ -2875,29 +2866,35 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="H3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
+        <v>14</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>21</v>
+      </c>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
@@ -2913,35 +2910,34 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B4" s="1" t="str">
-        <f>[1]myfunds_short_names!B4</f>
-        <v xml:space="preserve">BG Pacific</v>
+        <v>22</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="K4" s="1"/>
       <c r="L4" s="1"/>
@@ -2958,35 +2954,29 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>25</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="C5" s="1"/>
       <c r="D5" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>22</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
@@ -3002,35 +2992,31 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>22</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
@@ -3046,28 +3032,28 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
@@ -3086,29 +3072,35 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C8" s="1"/>
+        <v>40</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>41</v>
+      </c>
       <c r="D8" s="1" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>14</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
+        <v>14</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
@@ -3124,26 +3116,28 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C9" s="1"/>
+        <v>45</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>46</v>
+      </c>
       <c r="D9" s="1" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>14</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
@@ -3162,26 +3156,28 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C10" s="1"/>
+        <v>49</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>50</v>
+      </c>
       <c r="D10" s="1" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>14</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
@@ -3200,26 +3196,28 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C11" s="1"/>
+        <v>53</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>54</v>
+      </c>
       <c r="D11" s="1" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>14</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
@@ -3238,26 +3236,28 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C12" s="1"/>
+        <v>57</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>58</v>
+      </c>
       <c r="D12" s="1" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>14</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I12" s="1"/>
       <c r="J12" s="1"/>
@@ -3276,26 +3276,28 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C13" s="1"/>
+        <v>61</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>62</v>
+      </c>
       <c r="D13" s="1" t="s">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>14</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
@@ -3314,29 +3316,35 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="C14" s="1"/>
+        <v>65</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>66</v>
+      </c>
       <c r="D14" s="1" t="s">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>14</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I14" s="1"/>
-      <c r="J14" s="1"/>
+        <v>14</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="K14" s="1"/>
       <c r="L14" s="1"/>
       <c r="M14" s="1"/>
@@ -3352,29 +3360,35 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C15" s="1"/>
+        <v>69</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>70</v>
+      </c>
       <c r="D15" s="1" t="s">
-        <v>54</v>
+        <v>71</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>14</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I15" s="1"/>
-      <c r="J15" s="1"/>
+        <v>14</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="K15" s="1"/>
       <c r="L15" s="1"/>
       <c r="M15" s="1"/>
@@ -3390,26 +3404,28 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>55</v>
+        <v>73</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C16" s="1"/>
+        <v>74</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>75</v>
+      </c>
       <c r="D16" s="1" t="s">
-        <v>57</v>
+        <v>76</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>14</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
@@ -3428,29 +3444,36 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C17" s="1"/>
+        <v>77</v>
+      </c>
+      <c r="B17" s="1" t="e">
+        <f>#NAME?</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>78</v>
+      </c>
       <c r="D17" s="1" t="s">
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>14</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I17" s="1"/>
-      <c r="J17" s="1"/>
+        <v>14</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="K17" s="1"/>
       <c r="L17" s="1"/>
       <c r="M17" s="1"/>
@@ -3466,29 +3489,35 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="C18" s="1"/>
+        <v>82</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>83</v>
+      </c>
       <c r="D18" s="1" t="s">
-        <v>63</v>
+        <v>84</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>14</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I18" s="1"/>
-      <c r="J18" s="1"/>
+        <v>14</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="K18" s="1"/>
       <c r="L18" s="1"/>
       <c r="M18" s="1"/>
@@ -3504,26 +3533,28 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="s">
-        <v>64</v>
+        <v>86</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="C19" s="1"/>
+        <v>87</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>88</v>
+      </c>
       <c r="D19" s="1" t="s">
-        <v>66</v>
+        <v>89</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>14</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
@@ -3542,26 +3573,26 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="s">
-        <v>67</v>
+        <v>90</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C20" s="1"/>
-      <c r="D20" s="1" t="s">
-        <v>69</v>
-      </c>
+        <v>91</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D20" s="1"/>
       <c r="E20" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
@@ -3580,26 +3611,26 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="s">
-        <v>70</v>
+        <v>93</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="C21" s="1"/>
-      <c r="D21" s="1" t="s">
-        <v>72</v>
-      </c>
+        <v>94</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D21" s="1"/>
       <c r="E21" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>14</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
@@ -3618,29 +3649,35 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="s">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="C22" s="1"/>
+        <v>97</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>98</v>
+      </c>
       <c r="D22" s="1" t="s">
-        <v>75</v>
+        <v>99</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>14</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I22" s="1"/>
-      <c r="J22" s="1"/>
+        <v>14</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="J22" s="1" t="s">
+        <v>100</v>
+      </c>
       <c r="K22" s="1"/>
       <c r="L22" s="1"/>
       <c r="M22" s="1"/>
@@ -3656,31 +3693,35 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>76</v>
+        <v>101</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>77</v>
+        <v>102</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>78</v>
+        <v>103</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>79</v>
+        <v>104</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I23" s="1"/>
-      <c r="J23" s="1"/>
+        <v>14</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="K23" s="1"/>
       <c r="L23" s="1"/>
       <c r="M23" s="1"/>
@@ -3696,29 +3737,21 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>81</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="B24" s="1"/>
       <c r="C24" s="1"/>
-      <c r="D24" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="G24" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="H24" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I24" s="1"/>
-      <c r="J24" s="1"/>
+      <c r="D24" s="1"/>
+      <c r="E24" s="1"/>
+      <c r="F24" s="1"/>
+      <c r="G24" s="1"/>
+      <c r="H24" s="1"/>
+      <c r="I24" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="J24" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="K24" s="1"/>
       <c r="L24" s="1"/>
       <c r="M24" s="1"/>
@@ -3734,26 +3767,28 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="s">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="C25" s="1"/>
+        <v>108</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>109</v>
+      </c>
       <c r="D25" s="1" t="s">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>14</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I25" s="1"/>
       <c r="J25" s="1"/>
@@ -3772,26 +3807,26 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="s">
-        <v>86</v>
+        <v>111</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="C26" s="1"/>
-      <c r="D26" s="1" t="s">
-        <v>88</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="D26" s="1"/>
       <c r="E26" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>14</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I26" s="1"/>
       <c r="J26" s="1"/>
@@ -3810,29 +3845,34 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="C27" s="1"/>
-      <c r="D27" s="1" t="s">
-        <v>91</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="B27" s="1" t="e">
+        <f>#NAME?</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="D27" s="1"/>
       <c r="E27" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>14</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I27" s="1"/>
-      <c r="J27" s="1"/>
+        <v>14</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="J27" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="K27" s="1"/>
       <c r="L27" s="1"/>
       <c r="M27" s="1"/>
@@ -3848,26 +3888,26 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="s">
-        <v>92</v>
+        <v>116</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="C28" s="1"/>
-      <c r="D28" s="1" t="s">
-        <v>94</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="D28" s="1"/>
       <c r="E28" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>14</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I28" s="1"/>
       <c r="J28" s="1"/>
@@ -3886,29 +3926,35 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="s">
-        <v>95</v>
+        <v>119</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="C29" s="1"/>
+        <v>120</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>121</v>
+      </c>
       <c r="D29" s="1" t="s">
-        <v>97</v>
+        <v>122</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>14</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I29" s="1"/>
-      <c r="J29" s="1"/>
+        <v>14</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="J29" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="K29" s="1"/>
       <c r="L29" s="1"/>
       <c r="M29" s="1"/>
@@ -3924,26 +3970,28 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="s">
-        <v>98</v>
+        <v>124</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="C30" s="1"/>
+        <v>125</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>126</v>
+      </c>
       <c r="D30" s="1" t="s">
-        <v>100</v>
+        <v>127</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>14</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I30" s="1"/>
       <c r="J30" s="1"/>
@@ -3962,26 +4010,28 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>101</v>
+        <v>128</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="C31" s="1"/>
+        <v>129</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>130</v>
+      </c>
       <c r="D31" s="1" t="s">
-        <v>103</v>
+        <v>131</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>14</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I31" s="1"/>
       <c r="J31" s="1"/>
@@ -4000,33 +4050,29 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="s">
-        <v>104</v>
+        <v>132</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="D32" s="1"/>
+        <v>133</v>
+      </c>
+      <c r="C32" s="1"/>
+      <c r="D32" s="1" t="s">
+        <v>134</v>
+      </c>
       <c r="E32" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G32" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I32" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="J32" s="1" t="s">
-        <v>22</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="I32" s="1"/>
+      <c r="J32" s="1"/>
       <c r="K32" s="1"/>
       <c r="L32" s="1"/>
       <c r="M32" s="1"/>
@@ -4042,26 +4088,26 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="s">
-        <v>108</v>
+        <v>135</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>109</v>
+        <v>136</v>
       </c>
       <c r="C33" s="1"/>
       <c r="D33" s="1" t="s">
-        <v>110</v>
+        <v>137</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I33" s="1"/>
       <c r="J33" s="1"/>
@@ -4080,26 +4126,28 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="s">
-        <v>111</v>
+        <v>138</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="C34" s="1"/>
+        <v>139</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>140</v>
+      </c>
       <c r="D34" s="1" t="s">
-        <v>113</v>
+        <v>141</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>14</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I34" s="1"/>
       <c r="J34" s="1"/>
@@ -4118,35 +4166,31 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="s">
-        <v>114</v>
+        <v>142</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>115</v>
+        <v>143</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>116</v>
+        <v>144</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>117</v>
+        <v>145</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G35" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I35" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="J35" s="1" t="s">
-        <v>118</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="I35" s="1"/>
+      <c r="J35" s="1"/>
       <c r="K35" s="1"/>
       <c r="L35" s="1"/>
       <c r="M35" s="1"/>
@@ -4162,31 +4206,35 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="s">
-        <v>119</v>
+        <v>146</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>120</v>
+        <v>147</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>121</v>
+        <v>148</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>122</v>
+        <v>149</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I36" s="1"/>
-      <c r="J36" s="1"/>
+        <v>14</v>
+      </c>
+      <c r="I36" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="J36" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="K36" s="1"/>
       <c r="L36" s="1"/>
       <c r="M36" s="1"/>
@@ -4202,28 +4250,26 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="s">
-        <v>123</v>
+        <v>150</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>125</v>
-      </c>
+        <v>151</v>
+      </c>
+      <c r="C37" s="1"/>
       <c r="D37" s="1" t="s">
-        <v>126</v>
+        <v>152</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I37" s="1"/>
       <c r="J37" s="1"/>
@@ -4242,19 +4288,19 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="s">
-        <v>127</v>
+        <v>153</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>128</v>
+        <v>154</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>129</v>
+        <v>155</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>130</v>
+        <v>156</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>14</v>
@@ -4263,14 +4309,10 @@
         <v>14</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I38" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="J38" s="1" t="s">
-        <v>118</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="I38" s="1"/>
+      <c r="J38" s="1"/>
       <c r="K38" s="1"/>
       <c r="L38" s="1"/>
       <c r="M38" s="1"/>
@@ -4286,28 +4328,26 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="s">
-        <v>131</v>
+        <v>157</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>133</v>
-      </c>
+        <v>158</v>
+      </c>
+      <c r="C39" s="1"/>
       <c r="D39" s="1" t="s">
-        <v>134</v>
+        <v>159</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I39" s="1"/>
       <c r="J39" s="1"/>
@@ -4326,25 +4366,23 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="s">
-        <v>135</v>
+        <v>160</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>137</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="C40" s="1"/>
       <c r="D40" s="1" t="s">
-        <v>138</v>
+        <v>162</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H40" s="1" t="s">
         <v>14</v>
@@ -4366,35 +4404,29 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="s">
-        <v>139</v>
+        <v>163</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>141</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="C41" s="1"/>
       <c r="D41" s="1" t="s">
-        <v>142</v>
+        <v>165</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G41" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I41" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="J41" s="1" t="s">
-        <v>22</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="I41" s="1"/>
+      <c r="J41" s="1"/>
       <c r="K41" s="1"/>
       <c r="L41" s="1"/>
       <c r="M41" s="1"/>
@@ -4410,25 +4442,23 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="s">
-        <v>144</v>
+        <v>166</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>146</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="C42" s="1"/>
       <c r="D42" s="1" t="s">
-        <v>147</v>
+        <v>168</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H42" s="1" t="s">
         <v>14</v>
@@ -4450,25 +4480,23 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="s">
-        <v>148</v>
+        <v>169</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>150</v>
-      </c>
+        <v>170</v>
+      </c>
+      <c r="C43" s="1"/>
       <c r="D43" s="1" t="s">
-        <v>151</v>
+        <v>171</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H43" s="1" t="s">
         <v>14</v>
@@ -4490,28 +4518,26 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="s">
-        <v>152</v>
+        <v>172</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>154</v>
-      </c>
+        <v>173</v>
+      </c>
+      <c r="C44" s="1"/>
       <c r="D44" s="1" t="s">
-        <v>155</v>
+        <v>174</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I44" s="1"/>
       <c r="J44" s="1"/>
@@ -4530,31 +4556,33 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="s">
-        <v>156</v>
+        <v>175</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>158</v>
-      </c>
+        <v>176</v>
+      </c>
+      <c r="C45" s="1"/>
       <c r="D45" s="1" t="s">
-        <v>159</v>
+        <v>177</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H45" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="I45" s="1"/>
-      <c r="J45" s="1"/>
+      <c r="I45" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="J45" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="K45" s="1"/>
       <c r="L45" s="1"/>
       <c r="M45" s="1"/>
@@ -4570,28 +4598,26 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>162</v>
-      </c>
+        <v>180</v>
+      </c>
+      <c r="C46" s="1"/>
       <c r="D46" s="1" t="s">
-        <v>163</v>
+        <v>181</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I46" s="1"/>
       <c r="J46" s="1"/>
@@ -4610,28 +4636,26 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="s">
-        <v>164</v>
+        <v>182</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>166</v>
-      </c>
+        <v>183</v>
+      </c>
+      <c r="C47" s="1"/>
       <c r="D47" s="1" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I47" s="1"/>
       <c r="J47" s="1"/>
@@ -4650,28 +4674,26 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="s">
-        <v>168</v>
+        <v>185</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>170</v>
-      </c>
+        <v>186</v>
+      </c>
+      <c r="C48" s="1"/>
       <c r="D48" s="1" t="s">
-        <v>171</v>
+        <v>187</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I48" s="1"/>
       <c r="J48" s="1"/>
@@ -4690,25 +4712,23 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="s">
-        <v>172</v>
+        <v>188</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>174</v>
-      </c>
+        <v>189</v>
+      </c>
+      <c r="C49" s="1"/>
       <c r="D49" s="1" t="s">
-        <v>175</v>
+        <v>190</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H49" s="1" t="s">
         <v>14</v>
@@ -4730,31 +4750,21 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="D50" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="E50" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F50" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G50" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="H50" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I50" s="1"/>
-      <c r="J50" s="1"/>
+        <v>191</v>
+      </c>
+      <c r="B50" s="1"/>
+      <c r="C50" s="1"/>
+      <c r="D50" s="1"/>
+      <c r="E50" s="1"/>
+      <c r="F50" s="1"/>
+      <c r="G50" s="1"/>
+      <c r="H50" s="1"/>
+      <c r="I50" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="J50" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="K50" s="1"/>
       <c r="L50" s="1"/>
       <c r="M50" s="1"/>
@@ -4770,28 +4780,26 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>182</v>
-      </c>
+        <v>193</v>
+      </c>
+      <c r="C51" s="1"/>
       <c r="D51" s="1" t="s">
-        <v>183</v>
+        <v>194</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I51" s="1"/>
       <c r="J51" s="1"/>
@@ -4810,28 +4818,26 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="s">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>186</v>
-      </c>
+        <v>196</v>
+      </c>
+      <c r="C52" s="1"/>
       <c r="D52" s="1" t="s">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I52" s="1"/>
       <c r="J52" s="1"/>
@@ -4850,35 +4856,29 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="C53" s="1" t="s">
-        <v>190</v>
-      </c>
+        <v>199</v>
+      </c>
+      <c r="C53" s="1"/>
       <c r="D53" s="1" t="s">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G53" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I53" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="J53" s="1" t="s">
-        <v>22</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="I53" s="1"/>
+      <c r="J53" s="1"/>
       <c r="K53" s="1"/>
       <c r="L53" s="1"/>
       <c r="M53" s="1"/>
@@ -4894,28 +4894,26 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>194</v>
-      </c>
+        <v>202</v>
+      </c>
+      <c r="C54" s="1"/>
       <c r="D54" s="1" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I54" s="1"/>
       <c r="J54" s="1"/>
@@ -4934,28 +4932,26 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>198</v>
-      </c>
+        <v>205</v>
+      </c>
+      <c r="C55" s="1"/>
       <c r="D55" s="1" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I55" s="1"/>
       <c r="J55" s="1"/>
@@ -4974,25 +4970,23 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="s">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="C56" s="1" t="s">
-        <v>202</v>
-      </c>
+        <v>208</v>
+      </c>
+      <c r="C56" s="1"/>
       <c r="D56" s="1" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H56" s="1" t="s">
         <v>14</v>
@@ -5014,28 +5008,26 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>206</v>
-      </c>
+        <v>211</v>
+      </c>
+      <c r="C57" s="1"/>
       <c r="D57" s="1" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I57" s="1"/>
       <c r="J57" s="1"/>
@@ -5054,28 +5046,26 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>210</v>
-      </c>
+        <v>214</v>
+      </c>
+      <c r="C58" s="1"/>
       <c r="D58" s="1" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I58" s="1"/>
       <c r="J58" s="1"/>
@@ -5094,35 +5084,29 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="C59" s="1" t="s">
-        <v>214</v>
-      </c>
+        <v>217</v>
+      </c>
+      <c r="C59" s="1"/>
       <c r="D59" s="1" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G59" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I59" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="J59" s="1" t="s">
-        <v>22</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="I59" s="1"/>
+      <c r="J59" s="1"/>
       <c r="K59" s="1"/>
       <c r="L59" s="1"/>
       <c r="M59" s="1"/>
@@ -5138,28 +5122,28 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I60" s="1"/>
       <c r="J60" s="1"/>
@@ -5178,34 +5162,34 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I61" s="1" t="s">
-        <v>143</v>
+        <v>227</v>
       </c>
       <c r="J61" s="1" t="s">
-        <v>22</v>
+        <v>227</v>
       </c>
       <c r="K61" s="1"/>
       <c r="L61" s="1"/>
@@ -5222,35 +5206,31 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="E62" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G62" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I62" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="J62" s="1" t="s">
-        <v>22</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="I62" s="1"/>
+      <c r="J62" s="1"/>
       <c r="K62" s="1"/>
       <c r="L62" s="1"/>
       <c r="M62" s="1"/>
@@ -5266,28 +5246,28 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I63" s="1"/>
       <c r="J63" s="1"/>
@@ -5306,31 +5286,35 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I64" s="1"/>
-      <c r="J64" s="1"/>
+        <v>15</v>
+      </c>
+      <c r="I64" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="J64" s="1" t="s">
+        <v>227</v>
+      </c>
       <c r="K64" s="1"/>
       <c r="L64" s="1"/>
       <c r="M64" s="1"/>
@@ -5346,28 +5330,26 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="C65" s="1" t="s">
-        <v>238</v>
-      </c>
+        <v>241</v>
+      </c>
+      <c r="C65" s="1"/>
       <c r="D65" s="1" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I65" s="1"/>
       <c r="J65" s="1"/>
@@ -5386,35 +5368,31 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G66" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I66" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="J66" s="1" t="s">
-        <v>22</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="I66" s="1"/>
+      <c r="J66" s="1"/>
       <c r="K66" s="1"/>
       <c r="L66" s="1"/>
       <c r="M66" s="1"/>
@@ -5430,26 +5408,28 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="D67" s="1"/>
+        <v>249</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>250</v>
+      </c>
       <c r="E67" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I67" s="1"/>
       <c r="J67" s="1"/>
@@ -5468,23 +5448,25 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="D68" s="1"/>
+        <v>253</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>254</v>
+      </c>
       <c r="E68" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H68" s="1" t="s">
         <v>14</v>
@@ -5506,29 +5488,35 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="D69" s="1"/>
+        <v>257</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>258</v>
+      </c>
       <c r="E69" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I69" s="1"/>
-      <c r="J69" s="1"/>
+        <v>14</v>
+      </c>
+      <c r="I69" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J69" s="1" t="s">
+        <v>21</v>
+      </c>
       <c r="K69" s="1"/>
       <c r="L69" s="1"/>
       <c r="M69" s="1"/>
@@ -5544,34 +5532,34 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I70" s="1" t="s">
-        <v>258</v>
+        <v>105</v>
       </c>
       <c r="J70" s="1" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="K70" s="1"/>
       <c r="L70" s="1"/>
@@ -5588,26 +5576,26 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D71" s="1"/>
       <c r="E71" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I71" s="1"/>
       <c r="J71" s="1"/>
@@ -5626,34 +5614,34 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H72" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I72" s="1" t="s">
-        <v>266</v>
+        <v>80</v>
       </c>
       <c r="J72" s="1" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="K72" s="1"/>
       <c r="L72" s="1"/>
@@ -5670,23 +5658,25 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="B73" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="B73" s="1" t="s">
+      <c r="C73" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="C73" s="1" t="s">
+      <c r="D73" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="D73" s="1"/>
       <c r="E73" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H73" s="1" t="s">
         <v>14</v>
@@ -5718,19 +5708,23 @@
       </c>
       <c r="D74" s="1"/>
       <c r="E74" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H74" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I74" s="1"/>
-      <c r="J74" s="1"/>
+        <v>14</v>
+      </c>
+      <c r="I74" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="J74" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="K74" s="1"/>
       <c r="L74" s="1"/>
       <c r="M74" s="1"/>
@@ -5753,33 +5747,29 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>274</v>
-      </c>
-      <c r="C75" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="D75" s="1"/>
+      <c r="C75" s="1"/>
+      <c r="D75" s="1" t="s">
+        <v>276</v>
+      </c>
       <c r="E75" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G75" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H75" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I75" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="J75" s="1" t="s">
-        <v>22</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="I75" s="1"/>
+      <c r="J75" s="1"/>
       <c r="K75" s="1"/>
       <c r="L75" s="1"/>
       <c r="M75" s="1"/>
@@ -5802,34 +5792,34 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I76" s="1" t="s">
-        <v>266</v>
+        <v>20</v>
       </c>
       <c r="J76" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K76" s="1"/>
       <c r="L76" s="1"/>
@@ -5853,34 +5843,34 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I77" s="1" t="s">
-        <v>266</v>
+        <v>123</v>
       </c>
       <c r="J77" s="1" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="K77" s="1"/>
       <c r="L77" s="1"/>
@@ -5897,34 +5887,34 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H78" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I78" s="1" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="J78" s="1" t="s">
-        <v>22</v>
+        <v>290</v>
       </c>
       <c r="K78" s="1"/>
       <c r="L78" s="1"/>
@@ -5941,34 +5931,29 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="B79" s="1" t="str">
-        <f>[1]myfunds_short_names!B9</f>
-        <v xml:space="preserve">Fidelity Global Tech</v>
+        <v>291</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>292</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="D79" s="1"/>
       <c r="E79" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G79" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H79" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I79" s="1" t="s">
-        <v>288</v>
-      </c>
-      <c r="J79" s="1" t="s">
-        <v>22</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="I79" s="1"/>
+      <c r="J79" s="1"/>
       <c r="K79" s="1"/>
       <c r="L79" s="1"/>
       <c r="M79" s="1"/>
@@ -5984,34 +5969,34 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H80" s="1" t="s">
         <v>14</v>
       </c>
       <c r="I80" s="1" t="s">
-        <v>295</v>
+        <v>20</v>
       </c>
       <c r="J80" s="1" t="s">
-        <v>295</v>
+        <v>21</v>
       </c>
       <c r="K80" s="1"/>
       <c r="L80" s="1"/>
@@ -6028,34 +6013,34 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H81" s="1" t="s">
         <v>14</v>
       </c>
       <c r="I81" s="1" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="J81" s="1" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="K81" s="1"/>
       <c r="L81" s="1"/>
@@ -6072,19 +6057,19 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>14</v>
@@ -6093,14 +6078,10 @@
         <v>14</v>
       </c>
       <c r="H82" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I82" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="J82" s="1" t="s">
-        <v>305</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="I82" s="1"/>
+      <c r="J82" s="1"/>
       <c r="K82" s="1"/>
       <c r="L82" s="1"/>
       <c r="M82" s="1"/>
@@ -6128,22 +6109,22 @@
         <v>309</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G83" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H83" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I83" s="1" t="s">
-        <v>304</v>
+        <v>123</v>
       </c>
       <c r="J83" s="1" t="s">
-        <v>305</v>
+        <v>27</v>
       </c>
       <c r="K83" s="1"/>
       <c r="L83" s="1"/>
@@ -6172,22 +6153,22 @@
         <v>313</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H84" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I84" s="1" t="s">
-        <v>304</v>
+        <v>80</v>
       </c>
       <c r="J84" s="1" t="s">
-        <v>305</v>
+        <v>27</v>
       </c>
       <c r="K84" s="1"/>
       <c r="L84" s="1"/>
@@ -6212,26 +6193,24 @@
       <c r="C85" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="D85" s="1" t="s">
-        <v>317</v>
-      </c>
+      <c r="D85" s="1"/>
       <c r="E85" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G85" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H85" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I85" s="1" t="s">
-        <v>304</v>
+        <v>43</v>
       </c>
       <c r="J85" s="1" t="s">
-        <v>305</v>
+        <v>27</v>
       </c>
       <c r="K85" s="1"/>
       <c r="L85" s="1"/>
@@ -6248,35 +6227,31 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="B86" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="B86" s="1" t="s">
+      <c r="C86" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="C86" s="1" t="s">
+      <c r="D86" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="D86" s="1" t="s">
-        <v>321</v>
-      </c>
       <c r="E86" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G86" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H86" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I86" s="1" t="s">
-        <v>322</v>
-      </c>
-      <c r="J86" s="1" t="s">
-        <v>22</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="I86" s="1"/>
+      <c r="J86" s="1"/>
       <c r="K86" s="1"/>
       <c r="L86" s="1"/>
       <c r="M86" s="1"/>
@@ -6292,34 +6267,34 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="C87" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="B87" s="1" t="s">
+      <c r="D87" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="C87" s="1" t="s">
-        <v>325</v>
-      </c>
-      <c r="D87" s="1" t="s">
-        <v>326</v>
-      </c>
       <c r="E87" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H87" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I87" s="1" t="s">
-        <v>322</v>
+        <v>289</v>
       </c>
       <c r="J87" s="1" t="s">
-        <v>22</v>
+        <v>290</v>
       </c>
       <c r="K87" s="1"/>
       <c r="L87" s="1"/>
@@ -6336,33 +6311,29 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C88" s="1"/>
       <c r="D88" s="1" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G88" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H88" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I88" s="1" t="s">
-        <v>330</v>
-      </c>
-      <c r="J88" s="1" t="s">
-        <v>22</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="I88" s="1"/>
+      <c r="J88" s="1"/>
       <c r="K88" s="1"/>
       <c r="L88" s="1"/>
       <c r="M88" s="1"/>
@@ -6378,35 +6349,29 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>332</v>
-      </c>
-      <c r="C89" s="1" t="s">
-        <v>333</v>
-      </c>
+        <v>329</v>
+      </c>
+      <c r="C89" s="1"/>
       <c r="D89" s="1" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G89" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H89" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I89" s="1" t="s">
-        <v>335</v>
-      </c>
-      <c r="J89" s="1" t="s">
-        <v>336</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="I89" s="1"/>
+      <c r="J89" s="1"/>
       <c r="K89" s="1"/>
       <c r="L89" s="1"/>
       <c r="M89" s="1"/>
@@ -6422,34 +6387,34 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H90" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I90" s="1" t="s">
-        <v>335</v>
+        <v>123</v>
       </c>
       <c r="J90" s="1" t="s">
-        <v>336</v>
+        <v>27</v>
       </c>
       <c r="K90" s="1"/>
       <c r="L90" s="1"/>
@@ -6466,35 +6431,31 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G91" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H91" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I91" s="1" t="s">
-        <v>335</v>
-      </c>
-      <c r="J91" s="1" t="s">
-        <v>336</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="I91" s="1"/>
+      <c r="J91" s="1"/>
       <c r="K91" s="1"/>
       <c r="L91" s="1"/>
       <c r="M91" s="1"/>
@@ -6510,20 +6471,34 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="s">
-        <v>345</v>
-      </c>
-      <c r="B92" s="1"/>
-      <c r="C92" s="1"/>
-      <c r="D92" s="1"/>
-      <c r="E92" s="1"/>
-      <c r="F92" s="1"/>
-      <c r="G92" s="1"/>
-      <c r="H92" s="1"/>
+        <v>339</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="D92" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="E92" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F92" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G92" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H92" s="1" t="s">
+        <v>14</v>
+      </c>
       <c r="I92" s="1" t="s">
-        <v>118</v>
+        <v>43</v>
       </c>
       <c r="J92" s="1" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="K92" s="1"/>
       <c r="L92" s="1"/>
@@ -6540,20 +6515,26 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="D93" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="B93" s="1"/>
-      <c r="C93" s="1"/>
-      <c r="D93" s="1"/>
       <c r="E93" s="1"/>
       <c r="F93" s="1"/>
       <c r="G93" s="1"/>
       <c r="H93" s="1"/>
       <c r="I93" s="1" t="s">
-        <v>143</v>
+        <v>227</v>
       </c>
       <c r="J93" s="1" t="s">
-        <v>22</v>
+        <v>227</v>
       </c>
       <c r="K93" s="1"/>
       <c r="L93" s="1"/>
@@ -6581,15 +6562,23 @@
       <c r="D94" s="1" t="s">
         <v>350</v>
       </c>
-      <c r="E94" s="1"/>
-      <c r="F94" s="1"/>
-      <c r="G94" s="1"/>
-      <c r="H94" s="1"/>
+      <c r="E94" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F94" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G94" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H94" s="1" t="s">
+        <v>14</v>
+      </c>
       <c r="I94" s="1" t="s">
-        <v>295</v>
+        <v>100</v>
       </c>
       <c r="J94" s="1" t="s">
-        <v>295</v>
+        <v>100</v>
       </c>
       <c r="K94" s="1"/>
       <c r="L94" s="1"/>
@@ -19997,7 +19986,7 @@
   </sheetData>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555596" footer="0.51180555555555596"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="4294967295" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <pageSetup paperSize="9" scale="100" firstPageNumber="2147483648" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
   <headerFooter/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
@@ -20038,7 +20027,7 @@
         <v>355</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3">
@@ -20046,7 +20035,7 @@
         <v>356</v>
       </c>
       <c r="C3" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4">
@@ -20054,7 +20043,7 @@
         <v>357</v>
       </c>
       <c r="C4" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5">
@@ -20064,12 +20053,12 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>225</v>
+        <v>307</v>
       </c>
     </row>
     <row r="8">
@@ -20085,7 +20074,7 @@
         <v>361</v>
       </c>
       <c r="C9" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10">
@@ -20129,7 +20118,7 @@
         <v>361</v>
       </c>
       <c r="C13" t="s">
-        <v>118</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14">
@@ -20212,7 +20201,7 @@
   </sheetData>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555596" footer="0.51180555555555596"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="4294967295" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <pageSetup paperSize="9" scale="100" firstPageNumber="2147483648" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
   <headerFooter/>
 </worksheet>
 </file>
@@ -20270,826 +20259,826 @@
         <v>387</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>374</v>
+        <v>388</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>374</v>
+        <v>389</v>
       </c>
       <c r="G2" s="1"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>114</v>
+        <v>390</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>115</v>
+        <v>391</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>116</v>
+        <v>392</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>117</v>
+        <v>393</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>118</v>
+        <v>374</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>118</v>
+        <v>374</v>
       </c>
       <c r="G3" s="1"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>127</v>
+        <v>96</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>128</v>
+        <v>97</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>129</v>
+        <v>98</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>130</v>
+        <v>99</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>118</v>
+        <v>100</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>118</v>
+        <v>100</v>
       </c>
       <c r="G4" s="1"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>284</v>
+        <v>347</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>285</v>
+        <v>348</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>286</v>
+        <v>349</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>287</v>
+        <v>350</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>288</v>
+        <v>100</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>22</v>
+        <v>100</v>
       </c>
       <c r="G5" s="1"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>276</v>
+        <v>22</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>277</v>
+        <v>23</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>278</v>
+        <v>24</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>279</v>
+        <v>25</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>266</v>
+        <v>26</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="G6" s="1"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>262</v>
+        <v>39</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>263</v>
+        <v>40</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>264</v>
+        <v>41</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>265</v>
+        <v>42</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>266</v>
+        <v>43</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="G7" s="1"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>240</v>
+        <v>64</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>241</v>
+        <v>65</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>242</v>
+        <v>66</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>243</v>
+        <v>67</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>244</v>
+        <v>43</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="G8" s="1"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>18</v>
+        <v>68</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>388</v>
+        <v>69</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>19</v>
+        <v>70</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>20</v>
+        <v>71</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>21</v>
+        <v>72</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="G9" s="1"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>254</v>
+        <v>77</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>255</v>
+        <v>394</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>256</v>
+        <v>78</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>257</v>
+        <v>79</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>258</v>
+        <v>80</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="G10" s="1"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>323</v>
+        <v>81</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>324</v>
+        <v>82</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>325</v>
+        <v>83</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>326</v>
+        <v>84</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>322</v>
+        <v>85</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="G11" s="1"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>345</v>
+        <v>101</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>389</v>
+        <v>102</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>390</v>
+        <v>103</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>118</v>
+        <v>105</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="G12" s="1"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>391</v>
+        <v>106</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>394</v>
+        <v>99</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>266</v>
+        <v>100</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="G13" s="1"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>289</v>
+        <v>397</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>290</v>
-      </c>
-      <c r="D14" s="1"/>
+        <v>399</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>400</v>
+      </c>
       <c r="E14" s="1" t="s">
-        <v>288</v>
+        <v>43</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
-        <v>212</v>
+        <v>114</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>213</v>
+        <v>401</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>215</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="D15" s="1"/>
       <c r="E15" s="1" t="s">
-        <v>143</v>
+        <v>26</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>139</v>
+        <v>119</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>141</v>
+        <v>121</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>142</v>
+        <v>122</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>143</v>
+        <v>123</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>346</v>
+        <v>146</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>396</v>
+        <v>147</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>397</v>
+        <v>148</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>398</v>
+        <v>149</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="G17" s="1"/>
       <c r="H17" s="1"/>
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
-        <v>399</v>
+        <v>191</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>330</v>
+        <v>273</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="G18" s="1"/>
       <c r="H18" s="1"/>
     </row>
     <row r="19">
       <c r="A19" s="1" t="s">
-        <v>318</v>
+        <v>405</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>319</v>
+        <v>406</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>320</v>
+        <v>407</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>321</v>
+        <v>408</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>322</v>
+        <v>178</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="G19" s="1"/>
       <c r="H19" s="1"/>
     </row>
     <row r="20">
       <c r="A20" s="1" t="s">
-        <v>23</v>
+        <v>259</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>24</v>
+        <v>260</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>25</v>
+        <v>261</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>26</v>
+        <v>262</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>21</v>
+        <v>105</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="G20" s="1"/>
       <c r="H20" s="1"/>
     </row>
     <row r="21">
       <c r="A21" s="1" t="s">
-        <v>104</v>
+        <v>266</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>105</v>
+        <v>267</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="D21" s="1"/>
+        <v>268</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>269</v>
+      </c>
       <c r="E21" s="1" t="s">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="G21" s="1"/>
       <c r="H21" s="1"/>
     </row>
     <row r="22">
       <c r="A22" s="1" t="s">
-        <v>220</v>
+        <v>270</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>221</v>
+        <v>271</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>223</v>
-      </c>
+        <v>272</v>
+      </c>
+      <c r="D22" s="1"/>
       <c r="E22" s="1" t="s">
-        <v>143</v>
+        <v>273</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="G22" s="1"/>
       <c r="H22" s="1"/>
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>224</v>
+        <v>281</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>225</v>
+        <v>282</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>226</v>
+        <v>283</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>227</v>
+        <v>284</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>143</v>
+        <v>123</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="G23" s="1"/>
       <c r="H23" s="1"/>
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="F24" s="1" t="s">
         <v>27</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>22</v>
       </c>
       <c r="G24" s="1"/>
       <c r="H24" s="1"/>
     </row>
     <row r="25">
       <c r="A25" s="1" t="s">
-        <v>273</v>
+        <v>310</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>274</v>
+        <v>311</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="D25" s="1"/>
+        <v>312</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>313</v>
+      </c>
       <c r="E25" s="1" t="s">
-        <v>266</v>
+        <v>80</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="G25" s="1"/>
       <c r="H25" s="1"/>
     </row>
     <row r="26">
       <c r="A26" s="1" t="s">
-        <v>188</v>
+        <v>314</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>189</v>
+        <v>315</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>191</v>
-      </c>
+        <v>316</v>
+      </c>
+      <c r="D26" s="1"/>
       <c r="E26" s="1" t="s">
-        <v>143</v>
+        <v>43</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="G26" s="1"/>
       <c r="H26" s="1"/>
     </row>
     <row r="27">
       <c r="A27" s="1" t="s">
-        <v>280</v>
+        <v>331</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>281</v>
+        <v>332</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>282</v>
+        <v>333</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>283</v>
+        <v>334</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>266</v>
+        <v>123</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="G27" s="1"/>
       <c r="H27" s="1"/>
     </row>
     <row r="28">
       <c r="A28" s="1" t="s">
-        <v>291</v>
+        <v>339</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>292</v>
+        <v>340</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>293</v>
+        <v>341</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>294</v>
+        <v>342</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>295</v>
+        <v>43</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>295</v>
+        <v>27</v>
       </c>
       <c r="G28" s="1"/>
       <c r="H28" s="1"/>
     </row>
     <row r="29">
       <c r="A29" s="1" t="s">
-        <v>296</v>
+        <v>409</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>297</v>
+        <v>410</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>299</v>
-      </c>
+        <v>411</v>
+      </c>
+      <c r="D29" s="1"/>
       <c r="E29" s="1" t="s">
-        <v>295</v>
+        <v>80</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>295</v>
+        <v>27</v>
       </c>
       <c r="G29" s="1"/>
       <c r="H29" s="1"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="s">
-        <v>337</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>338</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>339</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>340</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>335</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>336</v>
+      <c r="A30" s="7" t="s">
+        <v>412</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>413</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>414</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>415</v>
+      </c>
+      <c r="E30" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="F30" s="7" t="s">
+        <v>27</v>
       </c>
       <c r="G30" s="1"/>
       <c r="H30" s="1"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="s">
-        <v>331</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>332</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>333</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>334</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>335</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>336</v>
-      </c>
-      <c r="G31" s="1"/>
+      <c r="A31" s="7" t="s">
+        <v>416</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>417</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>418</v>
+      </c>
+      <c r="D31" s="7"/>
+      <c r="E31" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="F31" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="G31" s="7"/>
       <c r="H31" s="1"/>
     </row>
     <row r="32">
       <c r="A32" s="1" t="s">
-        <v>341</v>
+        <v>223</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>342</v>
+        <v>224</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>343</v>
+        <v>225</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>344</v>
+        <v>226</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>335</v>
+        <v>227</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>336</v>
+        <v>227</v>
       </c>
       <c r="G32" s="1"/>
       <c r="H32" s="1"/>
     </row>
     <row r="33">
       <c r="A33" s="1" t="s">
-        <v>403</v>
+        <v>236</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>404</v>
+        <v>237</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>405</v>
+        <v>238</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>406</v>
+        <v>239</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>407</v>
+        <v>227</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>408</v>
+        <v>227</v>
       </c>
       <c r="G33" s="1"/>
       <c r="H33" s="1"/>
     </row>
     <row r="34">
       <c r="A34" s="1" t="s">
-        <v>306</v>
+        <v>285</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>307</v>
+        <v>286</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>308</v>
+        <v>287</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>309</v>
+        <v>288</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>304</v>
+        <v>289</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>305</v>
+        <v>290</v>
       </c>
       <c r="G34" s="1"/>
       <c r="H34" s="1"/>
     </row>
     <row r="35">
       <c r="A35" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="C35" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="B35" s="1" t="s">
+      <c r="D35" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="C35" s="1" t="s">
-        <v>302</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>303</v>
-      </c>
       <c r="E35" s="1" t="s">
-        <v>304</v>
+        <v>289</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>305</v>
+        <v>290</v>
       </c>
       <c r="G35" s="1"/>
       <c r="H35" s="1"/>
     </row>
     <row r="36">
       <c r="A36" s="1" t="s">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>304</v>
+        <v>289</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>305</v>
+        <v>290</v>
       </c>
       <c r="G36" s="1"/>
       <c r="H36" s="1"/>
     </row>
     <row r="37">
       <c r="A37" s="1" t="s">
-        <v>310</v>
+        <v>16</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>311</v>
+        <v>17</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>312</v>
+        <v>18</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>313</v>
+        <v>19</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>304</v>
+        <v>20</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>305</v>
+        <v>21</v>
       </c>
       <c r="G37" s="1"/>
       <c r="H37" s="1"/>
     </row>
     <row r="38">
       <c r="A38" s="1" t="s">
-        <v>409</v>
+        <v>255</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>410</v>
+        <v>256</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>411</v>
-      </c>
-      <c r="D38" s="1"/>
+        <v>257</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>258</v>
+      </c>
       <c r="E38" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F38" s="1" t="s">
         <v>21</v>
-      </c>
-      <c r="F38" s="1" t="s">
-        <v>22</v>
       </c>
       <c r="G38" s="1"/>
       <c r="H38" s="1"/>
     </row>
     <row r="39">
-      <c r="A39" s="7" t="s">
-        <v>412</v>
-      </c>
-      <c r="B39" s="7" t="s">
-        <v>413</v>
-      </c>
-      <c r="C39" s="7" t="s">
-        <v>414</v>
-      </c>
-      <c r="D39" s="7" t="s">
-        <v>415</v>
-      </c>
-      <c r="E39" s="7" t="s">
+      <c r="A39" s="8" t="s">
+        <v>277</v>
+      </c>
+      <c r="B39" s="8" t="s">
+        <v>278</v>
+      </c>
+      <c r="C39" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="D39" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="E39" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="F39" s="8" t="s">
         <v>21</v>
-      </c>
-      <c r="F39" s="7" t="s">
-        <v>22</v>
       </c>
       <c r="G39" s="1"/>
       <c r="H39" s="1"/>
     </row>
     <row r="40">
-      <c r="A40" s="7" t="s">
-        <v>416</v>
-      </c>
-      <c r="B40" s="7" t="s">
-        <v>417</v>
-      </c>
-      <c r="C40" s="7" t="s">
-        <v>418</v>
-      </c>
-      <c r="D40" s="7"/>
-      <c r="E40" s="7" t="s">
+      <c r="A40" s="8" t="s">
+        <v>294</v>
+      </c>
+      <c r="B40" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="C40" s="8" t="s">
+        <v>296</v>
+      </c>
+      <c r="D40" s="8" t="s">
+        <v>297</v>
+      </c>
+      <c r="E40" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="F40" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="F40" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="G40" s="7"/>
+      <c r="G40" s="8"/>
       <c r="H40" s="1"/>
     </row>
     <row r="41">
@@ -21105,7 +21094,7 @@
   </sheetData>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555596" footer="0.51180555555555596"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="4294967295" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <pageSetup paperSize="9" scale="100" firstPageNumber="2147483648" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
   <headerFooter/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
@@ -21218,7 +21207,7 @@
       <c r="B14" t="s">
         <v>441</v>
       </c>
-      <c r="D14" s="8">
+      <c r="D14" s="9">
         <v>0.29999999999999999</v>
       </c>
     </row>
@@ -21229,7 +21218,7 @@
       <c r="B15" t="s">
         <v>443</v>
       </c>
-      <c r="D15" s="8">
+      <c r="D15" s="9">
         <v>0.40000000000000002</v>
       </c>
     </row>
@@ -21240,7 +21229,7 @@
       <c r="B16" t="s">
         <v>445</v>
       </c>
-      <c r="D16" s="8">
+      <c r="D16" s="9">
         <v>0.14999999999999999</v>
       </c>
     </row>
@@ -21251,7 +21240,7 @@
       <c r="B17" t="s">
         <v>447</v>
       </c>
-      <c r="D17" s="8">
+      <c r="D17" s="9">
         <v>8.0000000000000002e-02</v>
       </c>
     </row>
@@ -21262,7 +21251,7 @@
       <c r="B18" t="s">
         <v>437</v>
       </c>
-      <c r="D18" s="8">
+      <c r="D18" s="9">
         <v>7.0000000000000007e-02</v>
       </c>
     </row>
@@ -21285,7 +21274,7 @@
       <c r="C22" t="s">
         <v>451</v>
       </c>
-      <c r="D22" s="8">
+      <c r="D22" s="9">
         <v>0.10000000000000001</v>
       </c>
       <c r="E22" s="2" t="s">
@@ -21302,7 +21291,7 @@
       <c r="C23" t="s">
         <v>455</v>
       </c>
-      <c r="D23" s="8">
+      <c r="D23" s="9">
         <v>0.10000000000000001</v>
       </c>
       <c r="E23" s="2" t="s">
@@ -21319,7 +21308,7 @@
       <c r="C24" t="s">
         <v>459</v>
       </c>
-      <c r="D24" s="8">
+      <c r="D24" s="9">
         <v>0.10000000000000001</v>
       </c>
       <c r="E24" s="2" t="s">
@@ -21336,7 +21325,7 @@
       <c r="C25" t="s">
         <v>463</v>
       </c>
-      <c r="D25" s="8">
+      <c r="D25" s="9">
         <v>0.10000000000000001</v>
       </c>
       <c r="E25" s="2" t="s">
@@ -21353,7 +21342,7 @@
       <c r="C26" t="s">
         <v>421</v>
       </c>
-      <c r="D26" s="8">
+      <c r="D26" s="9">
         <v>0.10000000000000001</v>
       </c>
       <c r="E26" s="2" t="s">
@@ -21370,7 +21359,7 @@
       <c r="C27" t="s">
         <v>470</v>
       </c>
-      <c r="D27" s="8">
+      <c r="D27" s="9">
         <v>0.10000000000000001</v>
       </c>
       <c r="E27" s="2" t="s">
@@ -21387,7 +21376,7 @@
       <c r="C28" t="s">
         <v>435</v>
       </c>
-      <c r="D28" s="8">
+      <c r="D28" s="9">
         <v>0.10000000000000001</v>
       </c>
       <c r="E28" s="2" t="s">
@@ -21404,7 +21393,7 @@
       <c r="C29" t="s">
         <v>433</v>
       </c>
-      <c r="D29" s="8">
+      <c r="D29" s="9">
         <v>0.10000000000000001</v>
       </c>
       <c r="E29" s="2" t="s">
@@ -21419,9 +21408,9 @@
         <v>447</v>
       </c>
       <c r="C30" t="s">
-        <v>130</v>
-      </c>
-      <c r="D30" s="8">
+        <v>350</v>
+      </c>
+      <c r="D30" s="9">
         <v>0.10000000000000001</v>
       </c>
       <c r="E30" s="2" t="s">
@@ -21438,7 +21427,7 @@
       <c r="C31" t="s">
         <v>439</v>
       </c>
-      <c r="D31" s="8">
+      <c r="D31" s="9">
         <v>0.10000000000000001</v>
       </c>
       <c r="E31" s="2" t="s">
@@ -21448,7 +21437,7 @@
   </sheetData>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555596" footer="0.51180555555555596"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="4294967295" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <pageSetup paperSize="9" scale="100" firstPageNumber="2147483648" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
   <headerFooter/>
 </worksheet>
 </file>